--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdfixincomevaluationtrade/TrdFixIncomeValuationTrade001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdfixincomevaluationtrade/TrdFixIncomeValuationTrade001.xlsx
@@ -16,11 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>交易份额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>交易编码</t>
     <rPh sb="0" eb="2">
@@ -72,23 +68,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>交易金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位净值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>币种</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>结算金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>资金账户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交割日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>会计分类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本金金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全价金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应收利息总额</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -444,58 +448,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="14.33203125" customWidth="1"/>
     <col min="4" max="7" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" style="1" customWidth="1"/>
-    <col min="9" max="10" width="14.33203125" customWidth="1"/>
-    <col min="11" max="14" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="14.33203125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="14.33203125" customWidth="1"/>
+    <col min="12" max="15" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
